--- a/business_surveys/031_recreational_vehicle_interest_survey--business_surveys.xlsx
+++ b/business_surveys/031_recreational_vehicle_interest_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2826,17 +2826,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>preferred_city_choices</t>
+          <t>desired_purchase_type_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>san_jose</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
@@ -2865,29 +2865,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>used</t>
+          <t>refurbished</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Used</t>
+          <t>Refurbished</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>desired_purchase_type_choices</t>
+          <t>preferred_make_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>refurbished</t>
+          <t>airstream</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Refurbished</t>
+          <t>Airstream</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>airstream</t>
+          <t>fleetwood</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Airstream</t>
+          <t>Fleetwood</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>fleetwood</t>
+          <t>jayco</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fleetwood</t>
+          <t>Jayco</t>
         </is>
       </c>
     </row>
@@ -2933,148 +2933,148 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jayco</t>
+          <t>jayco_jayflight</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jayco</t>
+          <t>Jayco JayFlight</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>preferred_make_choices</t>
+          <t>preferred_model_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jayco_jayflight</t>
+          <t>jay_flight_36</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jayco JayFlight</t>
+          <t>Jay Flight 36</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>preferred_make_choices</t>
+          <t>preferred_model_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jayco_jayflight</t>
+          <t>jay_flight_32</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jayco JayFlight</t>
+          <t>Jay Flight 32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>preferred_make_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jayco_jayflight</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jayco JayFlight</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>preferred_model_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jay_flight_36</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jay Flight 36</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>preferred_model_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jay_flight_36</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jay Flight 36</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>preferred_model_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jay_flight_32</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jay Flight 32</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>preferred_model_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jay_flight_32</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jay Flight 32</t>
+          <t>California</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>preferred_model_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jay_flight_32</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jay Flight 32</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>alabama</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>alaska</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>arizona</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>arkansas</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>california</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>colorado</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>connecticut</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>delaware</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>florida</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>georgia</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>hawaii</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>idaho</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>illinois</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>indiana</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>iowa</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kansas</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kentucky</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>louisiana</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>maine</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>maryland</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>massachusetts</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>michigan</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>minnesota</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>mississippi</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>missouri</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -3511,12 +3511,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>montana</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nebraska</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nevada</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>new_hampshire</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>new_jersey</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>new_mexico</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3613,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3630,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>north_carolina</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3647,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>north_dakota</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ohio</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3681,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>oklahoma</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>oregon</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>pennsylvania</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>rhode_island</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>south_carolina</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>south_dakota</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>tennessee</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>texas</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -3817,112 +3817,10 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>utah</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>vermont</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Vermont</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>virginia</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>washington</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>west_virginia</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>West Virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>wisconsin</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>wyoming</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
         <is>
           <t>Wyoming</t>
         </is>
